--- a/artfynd/A 38334-2023 artfynd.xlsx
+++ b/artfynd/A 38334-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38334-2023 artfynd.xlsx
+++ b/artfynd/A 38334-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -917,6 +917,380 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129727017</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91607</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Grötomsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>501304</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7037030</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Bo Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Bo Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129726999</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91583</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Grötomsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>501344</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7036965</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Bo Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Bo Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129727049</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Grötomsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>501380</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7036996</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påbörjat bohål i döende gran</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Bo Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Bo Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38334-2023 artfynd.xlsx
+++ b/artfynd/A 38334-2023 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>129727017</v>
       </c>
       <c r="B4" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>129726999</v>
       </c>
       <c r="B5" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>129727049</v>
       </c>
       <c r="B6" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 38334-2023 artfynd.xlsx
+++ b/artfynd/A 38334-2023 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>129727017</v>
       </c>
       <c r="B4" t="n">
-        <v>91608</v>
+        <v>91613</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>129726999</v>
       </c>
       <c r="B5" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38334-2023 artfynd.xlsx
+++ b/artfynd/A 38334-2023 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>129727017</v>
       </c>
       <c r="B4" t="n">
-        <v>91613</v>
+        <v>91617</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>129726999</v>
       </c>
       <c r="B5" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38334-2023 artfynd.xlsx
+++ b/artfynd/A 38334-2023 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>129727017</v>
       </c>
       <c r="B4" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>129726999</v>
       </c>
       <c r="B5" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38334-2023 artfynd.xlsx
+++ b/artfynd/A 38334-2023 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>129727017</v>
       </c>
       <c r="B4" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>129726999</v>
       </c>
       <c r="B5" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>129727049</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 38334-2023 artfynd.xlsx
+++ b/artfynd/A 38334-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>67820076</v>
       </c>
       <c r="B2" t="n">
-        <v>84993</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Clavaria zollingeri</t>
+          <t>Clavaria amethystina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Lév.</t>
+          <t>(Holmsk.) Bull.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>501360.3435597748</v>
+        <v>501360</v>
       </c>
       <c r="R2" t="n">
-        <v>7036955.177280893</v>
+        <v>7036955</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -758,19 +753,9 @@
           <t>2017-09-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-09-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -813,56 +798,62 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111781187</v>
+        <v>129726999</v>
       </c>
       <c r="B3" t="n">
-        <v>89845</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grötomsbodarna (Grötomsbodarna), Jmt</t>
+          <t>Grötomsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>501495</v>
+        <v>501344</v>
       </c>
       <c r="R3" t="n">
-        <v>7036929</v>
+        <v>7036965</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,12 +877,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,29 +891,43 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Bo Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Bo Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129727017</v>
+        <v>111781187</v>
       </c>
       <c r="B4" t="n">
-        <v>91648</v>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,47 +935,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grötomsbodarna, Jmt</t>
+          <t>Grötomsbodarna, Grötomsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501304</v>
+        <v>501495</v>
       </c>
       <c r="R4" t="n">
-        <v>7037030</v>
+        <v>7036929</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,12 +992,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,48 +1006,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo Persson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo Persson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129726999</v>
+        <v>129727049</v>
       </c>
       <c r="B5" t="n">
-        <v>91624</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,36 +1036,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1095,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501344</v>
+        <v>501380</v>
       </c>
       <c r="R5" t="n">
-        <v>7036965</v>
+        <v>7036996</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1133,6 +1102,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påbörjat bohål i döende gran</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1169,127 +1143,6 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>129727049</v>
-      </c>
-      <c r="B6" t="n">
-        <v>57740</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Grötomsbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>501380</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7036996</v>
-      </c>
-      <c r="S6" t="n">
-        <v>50</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Häggenås</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påbörjat bohål i döende gran</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Bo Persson</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Bo Persson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38334-2023 artfynd.xlsx
+++ b/artfynd/A 38334-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67820076</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -921,6 +931,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129726999</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1022,6 +1037,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111781187</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1143,8 +1163,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129727049</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>